--- a/Content/ProjectVD/DataTable/CharacterStats.xlsx
+++ b/Content/ProjectVD/DataTable/CharacterStats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thunderfury\ProjectVD\Content\ProjectVD\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17971B0D-4811-48B2-AEEA-3656F871631A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9E10B4-0B4C-4A11-9F6A-429B6809BE5D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>MaxHealth</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -40,6 +40,14 @@
   </si>
   <si>
     <t>AttackPower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -365,10 +373,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -381,8 +389,14 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -394,6 +408,12 @@
       </c>
       <c r="D2">
         <v>10</v>
+      </c>
+      <c r="E2">
+        <v>70</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Content/ProjectVD/DataTable/CharacterStats.xlsx
+++ b/Content/ProjectVD/DataTable/CharacterStats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thunderfury\ProjectVD\Content\ProjectVD\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9E10B4-0B4C-4A11-9F6A-429B6809BE5D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6F2232-DB75-4342-95AE-715D31900DF3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>MaxHealth</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -48,6 +48,14 @@
   </si>
   <si>
     <t>AttackSpeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxMovementSpeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinMovementAnalogSpeed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -373,10 +381,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -395,8 +403,14 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -414,6 +428,12 @@
       </c>
       <c r="F2">
         <v>1</v>
+      </c>
+      <c r="G2">
+        <v>400</v>
+      </c>
+      <c r="H2">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Content/ProjectVD/DataTable/CharacterStats.xlsx
+++ b/Content/ProjectVD/DataTable/CharacterStats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thunderfury\ProjectVD\Content\ProjectVD\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6F2232-DB75-4342-95AE-715D31900DF3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4C1257-8D76-4448-8EE7-58A1918C6B2A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>MaxHealth</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -56,6 +56,10 @@
   </si>
   <si>
     <t>MinMovementAnalogSpeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemyThreatRadius</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -381,10 +385,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -409,8 +413,11 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -434,6 +441,9 @@
       </c>
       <c r="H2">
         <v>25</v>
+      </c>
+      <c r="I2">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
